--- a/docs/templates/excel/Nelson-Liam-stage2-model.xlsx.xlsx
+++ b/docs/templates/excel/Nelson-Liam-stage2-model.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liamnelson/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B113ACCE-CF72-564F-AE0A-9AD2EF9D4325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5F614F-9AF0-AB41-9647-1DB5B8E2A87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5620" yWindow="1660" windowWidth="28200" windowHeight="19160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5620" yWindow="1660" windowWidth="28200" windowHeight="19160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transaction Hedging (Payables)" sheetId="1" r:id="rId1"/>
@@ -52,13 +52,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
   <si>
     <t>Hedging Foreign Currency Payables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suppose Boeing imported a Rolls-Royce jet engine for £5 million payable in one year
-</t>
   </si>
   <si>
     <t>Given</t>
@@ -1314,23 +1310,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1340,11 +1351,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1352,16 +1358,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1665,9 +1661,7 @@
     <row r="3" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="89" t="s">
-        <v>1</v>
-      </c>
+      <c r="C3" s="104"/>
       <c r="D3" s="90"/>
       <c r="E3" s="90"/>
       <c r="F3" s="90"/>
@@ -1731,17 +1725,17 @@
     <row r="5" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="113" t="s">
+      <c r="C5" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="6" t="s">
         <v>2</v>
-      </c>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="6" t="s">
-        <v>3</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="2"/>
@@ -1770,7 +1764,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="4"/>
       <c r="C6" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -1779,7 +1773,7 @@
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="84" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="2"/>
@@ -1808,7 +1802,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="4"/>
       <c r="C7" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
@@ -1817,7 +1811,7 @@
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="85" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="2"/>
@@ -1846,14 +1840,14 @@
       <c r="A8" s="1"/>
       <c r="B8" s="4"/>
       <c r="C8" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
       <c r="G8" s="9"/>
       <c r="H8" s="86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1882,7 +1876,7 @@
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
       <c r="C9" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
@@ -1918,7 +1912,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="4"/>
       <c r="C10" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
@@ -1954,7 +1948,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
       <c r="C11" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
@@ -1988,7 +1982,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
@@ -2024,7 +2018,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -2058,7 +2052,7 @@
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
@@ -2095,7 +2089,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="4"/>
       <c r="C15" s="23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
@@ -2162,16 +2156,16 @@
     <row r="17" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
-      <c r="C17" s="109" t="s">
-        <v>18</v>
+      <c r="C17" s="92" t="s">
+        <v>17</v>
       </c>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="105"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="94"/>
       <c r="K17" s="9"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2196,21 +2190,21 @@
     <row r="18" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1"/>
       <c r="B18" s="4"/>
-      <c r="C18" s="107" t="s">
-        <v>19</v>
+      <c r="C18" s="113" t="s">
+        <v>18</v>
       </c>
-      <c r="D18" s="93"/>
-      <c r="E18" s="108"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="114"/>
       <c r="F18" s="78">
         <f>contract_notional_value_payable*forward_price_payable</f>
         <v>4893750</v>
       </c>
-      <c r="G18" s="92" t="s">
-        <v>20</v>
+      <c r="G18" s="95" t="s">
+        <v>19</v>
       </c>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="94"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="97"/>
       <c r="K18" s="9"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2268,15 +2262,15 @@
       <c r="A20" s="1"/>
       <c r="B20" s="4"/>
       <c r="C20" s="103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="105"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="94"/>
       <c r="K20" s="9"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2301,8 +2295,8 @@
     <row r="21" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
-      <c r="C21" s="97" t="s">
-        <v>22</v>
+      <c r="C21" s="89" t="s">
+        <v>21</v>
       </c>
       <c r="D21" s="90"/>
       <c r="E21" s="91"/>
@@ -2310,10 +2304,10 @@
         <f>contract_notional_value_payable/(1+rate_uk_1y_payable)</f>
         <v>4377474.48905145</v>
       </c>
-      <c r="G21" s="101"/>
+      <c r="G21" s="110"/>
       <c r="H21" s="90"/>
       <c r="I21" s="90"/>
-      <c r="J21" s="102"/>
+      <c r="J21" s="111"/>
       <c r="K21" s="9"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2338,8 +2332,8 @@
     <row r="22" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1"/>
       <c r="B22" s="4"/>
-      <c r="C22" s="97" t="s">
-        <v>23</v>
+      <c r="C22" s="89" t="s">
+        <v>22</v>
       </c>
       <c r="D22" s="90"/>
       <c r="E22" s="91"/>
@@ -2347,10 +2341,10 @@
         <f>F21*current_spot_price_payable</f>
         <v>5041537.3690405544</v>
       </c>
-      <c r="G22" s="101"/>
+      <c r="G22" s="110"/>
       <c r="H22" s="90"/>
       <c r="I22" s="90"/>
-      <c r="J22" s="102"/>
+      <c r="J22" s="111"/>
       <c r="K22" s="9"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -2375,8 +2369,8 @@
     <row r="23" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="97" t="s">
-        <v>24</v>
+      <c r="C23" s="89" t="s">
+        <v>23</v>
       </c>
       <c r="D23" s="90"/>
       <c r="E23" s="91"/>
@@ -2412,8 +2406,8 @@
     <row r="24" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1"/>
       <c r="B24" s="4"/>
-      <c r="C24" s="97" t="s">
-        <v>25</v>
+      <c r="C24" s="89" t="s">
+        <v>24</v>
       </c>
       <c r="D24" s="90"/>
       <c r="E24" s="91"/>
@@ -2449,8 +2443,8 @@
     <row r="25" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1"/>
       <c r="B25" s="4"/>
-      <c r="C25" s="97" t="s">
-        <v>26</v>
+      <c r="C25" s="89" t="s">
+        <v>25</v>
       </c>
       <c r="D25" s="90"/>
       <c r="E25" s="91"/>
@@ -2458,10 +2452,10 @@
         <f>F22*(1+rate_us_1y_payable)</f>
         <v>5227065.9442212461</v>
       </c>
-      <c r="G25" s="101"/>
+      <c r="G25" s="110"/>
       <c r="H25" s="90"/>
       <c r="I25" s="90"/>
-      <c r="J25" s="102"/>
+      <c r="J25" s="111"/>
       <c r="K25" s="9"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2493,12 +2487,12 @@
         <f>F25</f>
         <v>5227065.9442212461</v>
       </c>
-      <c r="G26" s="92" t="s">
-        <v>20</v>
+      <c r="G26" s="95" t="s">
+        <v>19</v>
       </c>
-      <c r="H26" s="93"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="94"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="97"/>
       <c r="K26" s="9"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2556,15 +2550,15 @@
       <c r="A28" s="1"/>
       <c r="B28" s="4"/>
       <c r="C28" s="103" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="105"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="94"/>
       <c r="K28" s="9"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2589,8 +2583,8 @@
     <row r="29" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="4"/>
-      <c r="C29" s="97" t="s">
-        <v>28</v>
+      <c r="C29" s="89" t="s">
+        <v>27</v>
       </c>
       <c r="D29" s="90"/>
       <c r="E29" s="91"/>
@@ -2626,8 +2620,8 @@
     <row r="30" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
-      <c r="C30" s="97" t="s">
-        <v>29</v>
+      <c r="C30" s="89" t="s">
+        <v>28</v>
       </c>
       <c r="D30" s="90"/>
       <c r="E30" s="91"/>
@@ -2670,12 +2664,12 @@
         <f>MAX(G35:G47)</f>
         <v>5249368.08</v>
       </c>
-      <c r="G31" s="92" t="s">
-        <v>30</v>
+      <c r="G31" s="95" t="s">
+        <v>29</v>
       </c>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="94"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="97"/>
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -2732,24 +2726,24 @@
     <row r="33" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
-      <c r="C33" s="95" t="s">
+      <c r="C33" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="98" t="s">
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="100"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="106" t="s">
+      <c r="I33" s="109"/>
+      <c r="J33" s="108"/>
+      <c r="K33" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="I33" s="100"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="98" t="s">
-        <v>34</v>
-      </c>
-      <c r="L33" s="99"/>
+      <c r="L33" s="108"/>
       <c r="M33" s="9"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -2772,33 +2766,33 @@
     <row r="34" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
       <c r="B34" s="4"/>
-      <c r="C34" s="96"/>
+      <c r="C34" s="106"/>
       <c r="D34" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="39" t="s">
-        <v>18</v>
+      <c r="I34" s="43" t="s">
+        <v>20</v>
       </c>
-      <c r="F34" s="40" t="s">
-        <v>21</v>
+      <c r="J34" s="44" t="s">
+        <v>26</v>
       </c>
-      <c r="G34" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="42" t="s">
+      <c r="K34" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="I34" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="K34" s="38" t="s">
+      <c r="L34" s="45" t="s">
         <v>37</v>
-      </c>
-      <c r="L34" s="45" t="s">
-        <v>38</v>
       </c>
       <c r="M34" s="9"/>
       <c r="N34" s="2"/>
@@ -2821,8 +2815,8 @@
     </row>
     <row r="35" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="46"/>
-      <c r="B35" s="110" t="s">
-        <v>39</v>
+      <c r="B35" s="98" t="s">
+        <v>38</v>
       </c>
       <c r="C35" s="47">
         <f t="shared" ref="C35:C40" si="0">C36-0.05</f>
@@ -2865,7 +2859,7 @@
         <v>3. Option Hedge</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -2887,7 +2881,7 @@
     </row>
     <row r="36" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="46"/>
-      <c r="B36" s="111"/>
+      <c r="B36" s="99"/>
       <c r="C36" s="48">
         <f t="shared" si="0"/>
         <v>0.90169999999999972</v>
@@ -2949,7 +2943,7 @@
     </row>
     <row r="37" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="46"/>
-      <c r="B37" s="111"/>
+      <c r="B37" s="99"/>
       <c r="C37" s="48">
         <f t="shared" si="0"/>
         <v>0.95169999999999977</v>
@@ -3011,7 +3005,7 @@
     </row>
     <row r="38" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="46"/>
-      <c r="B38" s="111"/>
+      <c r="B38" s="99"/>
       <c r="C38" s="48">
         <f t="shared" si="0"/>
         <v>1.0016999999999998</v>
@@ -3073,7 +3067,7 @@
     </row>
     <row r="39" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="46"/>
-      <c r="B39" s="111"/>
+      <c r="B39" s="99"/>
       <c r="C39" s="48">
         <f t="shared" si="0"/>
         <v>1.0516999999999999</v>
@@ -3135,7 +3129,7 @@
     </row>
     <row r="40" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="46"/>
-      <c r="B40" s="111"/>
+      <c r="B40" s="99"/>
       <c r="C40" s="48">
         <f t="shared" si="0"/>
         <v>1.1016999999999999</v>
@@ -3197,7 +3191,7 @@
     </row>
     <row r="41" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="46"/>
-      <c r="B41" s="111"/>
+      <c r="B41" s="99"/>
       <c r="C41" s="48">
         <f>F7</f>
         <v>1.1516999999999999</v>
@@ -3239,7 +3233,7 @@
         <v>1. Forward Hedge</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -3261,7 +3255,7 @@
     </row>
     <row r="42" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="46"/>
-      <c r="B42" s="111"/>
+      <c r="B42" s="99"/>
       <c r="C42" s="48">
         <f t="shared" ref="C42:C47" si="10">C41+0.05</f>
         <v>1.2017</v>
@@ -3323,7 +3317,7 @@
     </row>
     <row r="43" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="46"/>
-      <c r="B43" s="111"/>
+      <c r="B43" s="99"/>
       <c r="C43" s="48">
         <f t="shared" si="10"/>
         <v>1.2517</v>
@@ -3385,7 +3379,7 @@
     </row>
     <row r="44" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="46"/>
-      <c r="B44" s="111"/>
+      <c r="B44" s="99"/>
       <c r="C44" s="48">
         <f t="shared" si="10"/>
         <v>1.3017000000000001</v>
@@ -3447,7 +3441,7 @@
     </row>
     <row r="45" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="46"/>
-      <c r="B45" s="111"/>
+      <c r="B45" s="99"/>
       <c r="C45" s="48">
         <f t="shared" si="10"/>
         <v>1.3517000000000001</v>
@@ -3509,7 +3503,7 @@
     </row>
     <row r="46" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="46"/>
-      <c r="B46" s="111"/>
+      <c r="B46" s="99"/>
       <c r="C46" s="48">
         <f t="shared" si="10"/>
         <v>1.4017000000000002</v>
@@ -3571,7 +3565,7 @@
     </row>
     <row r="47" spans="1:30" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="46"/>
-      <c r="B47" s="112"/>
+      <c r="B47" s="100"/>
       <c r="C47" s="51">
         <f t="shared" si="10"/>
         <v>1.4517000000000002</v>
@@ -3613,7 +3607,7 @@
         <v>1. Forward Hedge</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -34643,14 +34637,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="B35:B47"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C25:E25"/>
     <mergeCell ref="C3:J3"/>
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="C33:C34"/>
@@ -34667,6 +34653,14 @@
     <mergeCell ref="H33:J33"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="B35:B47"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C25:E25"/>
   </mergeCells>
   <conditionalFormatting sqref="D35:G47">
     <cfRule type="colorScale" priority="1">
@@ -34693,67 +34687,67 @@
   <sheetData>
     <row r="1" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="87" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A2" s="88" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A2" s="88" t="s">
+    <row r="3" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A3" s="88" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A3" s="88" t="s">
+    <row r="4" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A4" s="88" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A4" s="88" t="s">
+    <row r="5" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A5" s="88" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A5" s="88" t="s">
+    <row r="6" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A6" s="88" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A6" s="88" t="s">
+    <row r="7" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A7" s="88" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A7" s="88" t="s">
+    <row r="8" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A8" s="88" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A8" s="88" t="s">
+    <row r="9" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A9" s="88" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A9" s="88" t="s">
+    <row r="10" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A10" s="88" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A10" s="88" t="s">
+    <row r="11" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A11" s="88" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A11" s="88" t="s">
+    <row r="12" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A12" s="88" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A12" s="88" t="s">
-        <v>54</v>
-      </c>
-    </row>
     <row r="13" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A13" s="88" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
